--- a/SGC-CKN/Excel/ebeb5f45-bc6d-40ed-b179-dd374937df12_Hạng_mục_Lô_CT-02_P2-10_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/ebeb5f45-bc6d-40ed-b179-dd374937df12_Hạng_mục_Lô_CT-02_P2-10_D800_05-04-2026.xlsx
@@ -1154,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-3.6</v>
@@ -1163,10 +1163,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="J11" s="8">
-        <v>6.94</v>
+        <v>8.64</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-3.6</v>
@@ -1575,10 +1575,10 @@
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="I2" s="8">
-        <v>6.94</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.45</v>
@@ -1807,10 +1807,10 @@
         <v>11.42</v>
       </c>
       <c r="H10" s="33">
-        <v>43.74</v>
+        <v>44.45</v>
       </c>
       <c r="I10" s="33">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>
